--- a/tables/Player.xlsx
+++ b/tables/Player.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.25" customWidth="1" min="1" max="1"/>
@@ -740,11 +740,6 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
           <t>Note</t>
         </is>
       </c>
@@ -821,11 +816,6 @@
         <v>150</v>
       </c>
       <c r="W7" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="X7" s="4" t="inlineStr">
         <is>
           <t>CritHitStunTime=치명타 피격 경직, LandFallHeight=착지 모션이 나오는 낙하 높이(5타일), InputBuffer=선입력 버퍼</t>
         </is>

--- a/tables/Player.xlsx
+++ b/tables/Player.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>스태미나·구르기·점프·피격 경직·약초·매달리기·착지·선입력.</t>
+          <t>CSV,스태미나·구르기·점프·피격 경직·약초·매달리기·착지·선입력.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>

--- a/tables/Player.xlsx
+++ b/tables/Player.xlsx
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="R7" s="4" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="S7" s="4" t="n">
         <v>500</v>

--- a/tables/Player.xlsx
+++ b/tables/Player.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>한 행 = 플레이어 조작 프로필 하나. Regen은 초당, 시간은 ms, 거리는 타일×100.</t>
+          <t>한 행 = 플레이어 조작 프로필 하나. Regen은 초당, 시간은 ms, 거리는 타일×100. 1~3열(ID, Name, UnitID)은 Monster·BossState·EliteState와 같은 순서, 그 뒤는 플레이어 전용 열. 약초는 Buff 탭(14001)으로 분리(10/29).</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
@@ -507,7 +507,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>CSV,스태미나·구르기·점프·피격 경직·약초·매달리기·착지·선입력.</t>
+          <t>CSV,스태미나·구르기·점프·피격 경직·착지·매달리기·선입력·시작 무기.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -539,7 +539,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>플레이어 컨트롤러가 읽는다. UnitID는 UnitStat, StartWeapon은 Weapon ID.</t>
+          <t>플레이어 컨트롤러가 읽는다. UnitID는 UnitStat, StartWeapon은 Item ID.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>조작 감각을 프로필만 바꿔 비교하기 위해. 인벤토리는 지스타 제외(완성판), 약초 개수만 HUD 표시.</t>
+          <t>조작 감각을 프로필만 바꿔 비교하기 위해. 인벤토리는 지스타 제외(완성판), 약초 개수만 HUD 표시(Buff 14001 Charges).</t>
         </is>
       </c>
       <c r="C4" s="1" t="n"/>
@@ -695,17 +695,17 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>HerbHeal</t>
+          <t>CritHitStunTime</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>HerbCount</t>
+          <t>LandFallHeight</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>HerbUseTime</t>
+          <t>LandTime</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -715,34 +715,22 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
+          <t>InputBuffer</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
           <t>StartWeapon</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>CritHitStunTime</t>
-        </is>
-      </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>LandFallHeight</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>LandTime</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>InputBuffer</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr">
-        <is>
           <t>Note</t>
         </is>
       </c>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n"/>
+      <c r="W6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -787,13 +775,13 @@
         <v>600</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
@@ -801,21 +789,12 @@
         </is>
       </c>
       <c r="R7" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="S7" s="4" t="n">
         <v>6002</v>
       </c>
-      <c r="S7" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>CritHitStunTime=치명타 피격 경직, LandFallHeight=착지 모션이 나오는 낙하 높이(5타일), InputBuffer=선입력 버퍼</t>
         </is>

--- a/tables/Player.xlsx
+++ b/tables/Player.xlsx
@@ -436,371 +436,392 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:W7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10.25" customWidth="1" min="1" max="1"/>
-    <col width="6.25" customWidth="1" min="2" max="2"/>
-    <col width="10.13" customWidth="1" min="3" max="3"/>
-    <col width="11.63" customWidth="1" min="4" max="4"/>
-    <col width="15.63" customWidth="1" min="5" max="5"/>
-    <col width="10.13" customWidth="1" min="6" max="6"/>
-    <col width="7.5" customWidth="1" min="7" max="7"/>
-    <col width="8.880000000000001" customWidth="1" min="8" max="8"/>
-    <col width="9.75" customWidth="1" min="9" max="9"/>
-    <col width="9.880000000000001" customWidth="1" min="10" max="10"/>
-    <col width="10.13" customWidth="1" min="11" max="11"/>
-    <col width="8.130000000000001" customWidth="1" min="12" max="12"/>
-    <col width="7.75" customWidth="1" min="13" max="13"/>
-    <col width="8.880000000000001" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="8.25" customWidth="1" min="16" max="16"/>
-    <col width="10.38" customWidth="1" min="17" max="17"/>
-    <col width="12.75" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="8.25" customWidth="1" min="20" max="20"/>
-    <col width="9.25" customWidth="1" min="21" max="21"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>규칙</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>한 행 = 플레이어 조작 프로필 하나. Regen은 초당, 시간은 ms, 거리는 타일×100. 1~3열(ID, Name, UnitID)은 Monster·BossState·EliteState와 같은 순서, 그 뒤는 플레이어 전용 열. 약초는 Buff 탭(14001)으로 분리(10/29).</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>CSV,스태미나·구르기·점프·피격 경직·착지·매달리기·선입력·시작 무기.</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="n"/>
-      <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
-      <c r="N2" s="1" t="n"/>
-      <c r="O2" s="1" t="n"/>
-      <c r="P2" s="1" t="n"/>
-      <c r="Q2" s="1" t="n"/>
-      <c r="R2" s="1" t="n"/>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>플레이어 컨트롤러가 읽는다. UnitID는 UnitStat, StartWeapon은 Item ID.</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-      <c r="I3" s="1" t="n"/>
-      <c r="J3" s="1" t="n"/>
-      <c r="K3" s="1" t="n"/>
-      <c r="L3" s="1" t="n"/>
-      <c r="M3" s="1" t="n"/>
-      <c r="N3" s="1" t="n"/>
-      <c r="O3" s="1" t="n"/>
-      <c r="P3" s="1" t="n"/>
-      <c r="Q3" s="1" t="n"/>
-      <c r="R3" s="1" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>의도</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>조작 감각을 프로필만 바꿔 비교하기 위해. 인벤토리는 지스타 제외(완성판), 약초 개수만 HUD 표시(Buff 14001 Charges).</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-      <c r="J4" s="1" t="n"/>
-      <c r="K4" s="1" t="n"/>
-      <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
-      <c r="N4" s="1" t="n"/>
-      <c r="O4" s="1" t="n"/>
-      <c r="P4" s="1" t="n"/>
-      <c r="Q4" s="1" t="n"/>
-      <c r="R4" s="1" t="n"/>
-      <c r="S4" s="2" t="n"/>
-      <c r="T4" s="2" t="n"/>
-      <c r="U4" s="2" t="n"/>
-      <c r="V4" s="2" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Name, Note</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="n"/>
-      <c r="I5" s="1" t="n"/>
-      <c r="J5" s="1" t="n"/>
-      <c r="K5" s="1" t="n"/>
-      <c r="L5" s="1" t="n"/>
-      <c r="M5" s="1" t="n"/>
-      <c r="N5" s="1" t="n"/>
-      <c r="O5" s="1" t="n"/>
-      <c r="P5" s="1" t="n"/>
-      <c r="Q5" s="1" t="n"/>
-      <c r="R5" s="1" t="n"/>
-      <c r="S5" s="2" t="n"/>
-      <c r="T5" s="2" t="n"/>
-      <c r="U5" s="2" t="n"/>
-      <c r="V5" s="2" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>UnitID</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>StaminaMax</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>StaminaRegen</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>StaminaRegenDelay</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>RollDistance</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>RollTime</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>RollIFrame</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>RollStamina</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>JumpHeight</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>HitStunTime</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>HitIFrame</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>CritHitStunTime</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>LandFallHeight</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>LandTime</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>HangAuto</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t>InputBuffer</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>StartWeapon</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="n"/>
-      <c r="V6" s="3" t="n"/>
-      <c r="W6" s="3" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>막손 기본</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1001</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>600</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>6002</v>
-      </c>
-      <c r="T7" s="4" t="inlineStr">
-        <is>
-          <t>CritHitStunTime=치명타 피격 경직, LandFallHeight=착지 모션이 나오는 낙하 높이(5타일), InputBuffer=선입력 버퍼</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr>
+    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
+    <ns0:pageSetUpPr/>
+  </ns0:sheetPr>
+  <ns0:dimension ref="A1:W7"/>
+  <ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <ns0:cols>
+    <ns0:col width="10.25" customWidth="1" min="1" max="1"/>
+    <ns0:col width="6.25" customWidth="1" min="2" max="2"/>
+    <ns0:col width="10.13" customWidth="1" min="3" max="3"/>
+    <ns0:col width="11.63" customWidth="1" min="4" max="4"/>
+    <ns0:col width="15.63" customWidth="1" min="5" max="5"/>
+    <ns0:col width="10.13" customWidth="1" min="6" max="6"/>
+    <ns0:col width="7.5" customWidth="1" min="7" max="7"/>
+    <ns0:col width="8.880000000000001" customWidth="1" min="8" max="8"/>
+    <ns0:col width="9.75" customWidth="1" min="9" max="9"/>
+    <ns0:col width="9.880000000000001" customWidth="1" min="10" max="10"/>
+    <ns0:col width="10.13" customWidth="1" min="11" max="11"/>
+    <ns0:col width="8.130000000000001" customWidth="1" min="12" max="12"/>
+    <ns0:col width="7.75" customWidth="1" min="13" max="13"/>
+    <ns0:col width="8.880000000000001" customWidth="1" min="14" max="14"/>
+    <ns0:col width="11" customWidth="1" min="15" max="15"/>
+    <ns0:col width="8.25" customWidth="1" min="16" max="16"/>
+    <ns0:col width="10.38" customWidth="1" min="17" max="17"/>
+    <ns0:col width="12.75" customWidth="1" min="18" max="18"/>
+    <ns0:col width="12" customWidth="1" min="19" max="19"/>
+    <ns0:col width="8.25" customWidth="1" min="20" max="20"/>
+    <ns0:col width="9.25" customWidth="1" min="21" max="21"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1">
+      <ns0:c r="A1" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>규칙</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B1" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">한 행 = 플레이어 조작 프로필 하나. Regen은 초당, 시간은 ms, 거리는 타일×100. 1~3열(ID, Name, UnitID)은 Monster·BossState·EliteState와 같은 순서, 그 뒤는 플레이어 전용 열. 약초는 Buff 탭(14001)으로 분리(10/29).
+[추출 지정 규칙]
+@column Name=UnitID;Type=Integer;Minimum=1;ReferenceTable=UnitStat
+@column Name=StaminaMax;Type=Integer;Minimum=0
+@column Name=StaminaRegen;Type=Integer;Minimum=0;Unit=per_second
+@column Name=StaminaRegenDelay;Type=Integer;Minimum=0;Unit=ms
+@column Name=RollDistance;Type=Integer;Minimum=0;Unit=tile_x100
+@column Name=RollTime;Type=Integer;Minimum=0;Unit=ms
+@column Name=RollIFrame;Type=Integer;Minimum=0;Unit=ms
+@column Name=RollStamina;Type=Integer;Minimum=0
+@column Name=JumpHeight;Type=Integer;Minimum=0;Unit=tile_x100
+@column Name=HitStunTime;Type=Integer;Minimum=0;Unit=ms
+@column Name=HitIFrame;Type=Integer;Minimum=0;Unit=ms
+@column Name=CritHitStunTime;Type=Integer;Minimum=0;Unit=ms
+@column Name=LandFallHeight;Type=Integer;Minimum=0;Unit=tile_x100
+@column Name=LandTime;Type=Integer;Minimum=0;Unit=ms
+@column Name=HangAuto;Type=Flag
+@column Name=InputBuffer;Type=Integer;Minimum=0;Unit=ms
+@column Name=StartWeapon;Type=Integer;Minimum=1;ReferenceTable=Item
+@check Kind=ReferenceValue;Column=UnitID;Table=UnitStat;TargetColumn=Type;Value=Player;Code=UNIT_TYPE
+@check Kind=ReferenceValue;Column=StartWeapon;Table=Item;TargetColumn=ItemType;Value=Weapon;Code=ITEM_TYPE
+@inherit Base=CharacterStat</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C1" s="1" t="n"/>
+      <ns0:c r="D1" s="1" t="n"/>
+      <ns0:c r="E1" s="1" t="n"/>
+      <ns0:c r="F1" s="1" t="n"/>
+      <ns0:c r="G1" s="1" t="n"/>
+      <ns0:c r="H1" s="1" t="n"/>
+      <ns0:c r="I1" s="1" t="n"/>
+      <ns0:c r="J1" s="1" t="n"/>
+      <ns0:c r="K1" s="1" t="n"/>
+      <ns0:c r="L1" s="1" t="n"/>
+      <ns0:c r="M1" s="1" t="n"/>
+      <ns0:c r="N1" s="1" t="n"/>
+      <ns0:c r="O1" s="1" t="n"/>
+      <ns0:c r="P1" s="1" t="n"/>
+      <ns0:c r="Q1" s="1" t="n"/>
+      <ns0:c r="R1" s="1" t="n"/>
+      <ns0:c r="S1" s="2" t="n"/>
+      <ns0:c r="T1" s="2" t="n"/>
+      <ns0:c r="U1" s="2" t="n"/>
+      <ns0:c r="V1" s="2" t="n"/>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>기능</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B2" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CSV,스태미나·구르기·점프·피격 경직·착지·매달리기·선입력·시작 무기.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C2" s="1" t="n"/>
+      <ns0:c r="D2" s="1" t="n"/>
+      <ns0:c r="E2" s="1" t="n"/>
+      <ns0:c r="F2" s="1" t="n"/>
+      <ns0:c r="G2" s="1" t="n"/>
+      <ns0:c r="H2" s="1" t="n"/>
+      <ns0:c r="I2" s="1" t="n"/>
+      <ns0:c r="J2" s="1" t="n"/>
+      <ns0:c r="K2" s="1" t="n"/>
+      <ns0:c r="L2" s="1" t="n"/>
+      <ns0:c r="M2" s="1" t="n"/>
+      <ns0:c r="N2" s="1" t="n"/>
+      <ns0:c r="O2" s="1" t="n"/>
+      <ns0:c r="P2" s="1" t="n"/>
+      <ns0:c r="Q2" s="1" t="n"/>
+      <ns0:c r="R2" s="1" t="n"/>
+      <ns0:c r="S2" s="2" t="n"/>
+      <ns0:c r="T2" s="2" t="n"/>
+      <ns0:c r="U2" s="2" t="n"/>
+      <ns0:c r="V2" s="2" t="n"/>
+    </ns0:row>
+    <ns0:row r="3">
+      <ns0:c r="A3" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>역할</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B3" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>플레이어 컨트롤러가 읽는다. UnitID는 UnitStat, StartWeapon은 Item ID.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C3" s="1" t="n"/>
+      <ns0:c r="D3" s="1" t="n"/>
+      <ns0:c r="E3" s="1" t="n"/>
+      <ns0:c r="F3" s="1" t="n"/>
+      <ns0:c r="G3" s="1" t="n"/>
+      <ns0:c r="H3" s="1" t="n"/>
+      <ns0:c r="I3" s="1" t="n"/>
+      <ns0:c r="J3" s="1" t="n"/>
+      <ns0:c r="K3" s="1" t="n"/>
+      <ns0:c r="L3" s="1" t="n"/>
+      <ns0:c r="M3" s="1" t="n"/>
+      <ns0:c r="N3" s="1" t="n"/>
+      <ns0:c r="O3" s="1" t="n"/>
+      <ns0:c r="P3" s="1" t="n"/>
+      <ns0:c r="Q3" s="1" t="n"/>
+      <ns0:c r="R3" s="1" t="n"/>
+      <ns0:c r="S3" s="2" t="n"/>
+      <ns0:c r="T3" s="2" t="n"/>
+      <ns0:c r="U3" s="2" t="n"/>
+      <ns0:c r="V3" s="2" t="n"/>
+    </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="A4" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>의도</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B4" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>조작 감각을 프로필만 바꿔 비교하기 위해. 인벤토리는 지스타 제외(완성판), 약초 개수만 HUD 표시(Buff 14001 Charges).</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C4" s="1" t="n"/>
+      <ns0:c r="D4" s="1" t="n"/>
+      <ns0:c r="E4" s="1" t="n"/>
+      <ns0:c r="F4" s="1" t="n"/>
+      <ns0:c r="G4" s="1" t="n"/>
+      <ns0:c r="H4" s="1" t="n"/>
+      <ns0:c r="I4" s="1" t="n"/>
+      <ns0:c r="J4" s="1" t="n"/>
+      <ns0:c r="K4" s="1" t="n"/>
+      <ns0:c r="L4" s="1" t="n"/>
+      <ns0:c r="M4" s="1" t="n"/>
+      <ns0:c r="N4" s="1" t="n"/>
+      <ns0:c r="O4" s="1" t="n"/>
+      <ns0:c r="P4" s="1" t="n"/>
+      <ns0:c r="Q4" s="1" t="n"/>
+      <ns0:c r="R4" s="1" t="n"/>
+      <ns0:c r="S4" s="2" t="n"/>
+      <ns0:c r="T4" s="2" t="n"/>
+      <ns0:c r="U4" s="2" t="n"/>
+      <ns0:c r="V4" s="2" t="n"/>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="A5" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>비고</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B5" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Name, Note</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C5" s="1" t="n"/>
+      <ns0:c r="D5" s="1" t="n"/>
+      <ns0:c r="E5" s="1" t="n"/>
+      <ns0:c r="F5" s="1" t="n"/>
+      <ns0:c r="G5" s="1" t="n"/>
+      <ns0:c r="H5" s="1" t="n"/>
+      <ns0:c r="I5" s="1" t="n"/>
+      <ns0:c r="J5" s="1" t="n"/>
+      <ns0:c r="K5" s="1" t="n"/>
+      <ns0:c r="L5" s="1" t="n"/>
+      <ns0:c r="M5" s="1" t="n"/>
+      <ns0:c r="N5" s="1" t="n"/>
+      <ns0:c r="O5" s="1" t="n"/>
+      <ns0:c r="P5" s="1" t="n"/>
+      <ns0:c r="Q5" s="1" t="n"/>
+      <ns0:c r="R5" s="1" t="n"/>
+      <ns0:c r="S5" s="2" t="n"/>
+      <ns0:c r="T5" s="2" t="n"/>
+      <ns0:c r="U5" s="2" t="n"/>
+      <ns0:c r="V5" s="2" t="n"/>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Name</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>UnitID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>StaminaMax</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>StaminaRegen</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>StaminaRegenDelay</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>RollDistance</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>RollTime</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>RollIFrame</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>RollStamina</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>JumpHeight</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>HitStunTime</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="M6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>HitIFrame</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="N6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CritHitStunTime</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="O6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>LandFallHeight</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="P6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>LandTime</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>HangAuto</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>InputBuffer</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="S6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>StartWeapon</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T6" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Note</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="U6" s="3" t="n"/>
+      <ns0:c r="V6" s="3" t="n"/>
+      <ns0:c r="W6" s="3" t="n"/>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7" s="4" t="n">
+        <ns0:v>2001</ns0:v>
+      </ns0:c>
+      <ns0:c r="B7" s="4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>막손 기본</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C7" s="4" t="n">
+        <ns0:v>1001</ns0:v>
+      </ns0:c>
+      <ns0:c r="D7" s="4" t="n">
+        <ns0:v>100</ns0:v>
+      </ns0:c>
+      <ns0:c r="E7" s="4" t="n">
+        <ns0:v>45</ns0:v>
+      </ns0:c>
+      <ns0:c r="F7" s="4" t="n">
+        <ns0:v>500</ns0:v>
+      </ns0:c>
+      <ns0:c r="G7" s="4" t="n">
+        <ns0:v>300</ns0:v>
+      </ns0:c>
+      <ns0:c r="H7" s="4" t="n">
+        <ns0:v>500</ns0:v>
+      </ns0:c>
+      <ns0:c r="I7" s="4" t="n">
+        <ns0:v>300</ns0:v>
+      </ns0:c>
+      <ns0:c r="J7" s="4" t="n">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="K7" s="4" t="n">
+        <ns0:v>300</ns0:v>
+      </ns0:c>
+      <ns0:c r="L7" s="4" t="n">
+        <ns0:v>300</ns0:v>
+      </ns0:c>
+      <ns0:c r="M7" s="4" t="n">
+        <ns0:v>600</ns0:v>
+      </ns0:c>
+      <ns0:c r="N7" s="4" t="n">
+        <ns0:v>500</ns0:v>
+      </ns0:c>
+      <ns0:c r="O7" s="4" t="n">
+        <ns0:v>500</ns0:v>
+      </ns0:c>
+      <ns0:c r="P7" s="4" t="n">
+        <ns0:v>200</ns0:v>
+      </ns0:c>
+      <ns0:c r="Q7" s="4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Y</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R7" s="4" t="n">
+        <ns0:v>150</ns0:v>
+      </ns0:c>
+      <ns0:c r="S7" s="4" t="n">
+        <ns0:v>6002</ns0:v>
+      </ns0:c>
+      <ns0:c r="T7" s="4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CritHitStunTime=치명타 피격 경직, LandFallHeight=착지 모션이 나오는 낙하 높이(5타일), InputBuffer=선입력 버퍼</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</ns0:worksheet>
 </file>
--- a/tables/Player.xlsx
+++ b/tables/Player.xlsx
@@ -436,46 +436,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:sheetPr>
-    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
-    <ns0:pageSetUpPr/>
-  </ns0:sheetPr>
-  <ns0:dimension ref="A1:W7"/>
-  <ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <ns0:cols>
-    <ns0:col width="10.25" customWidth="1" min="1" max="1"/>
-    <ns0:col width="6.25" customWidth="1" min="2" max="2"/>
-    <ns0:col width="10.13" customWidth="1" min="3" max="3"/>
-    <ns0:col width="11.63" customWidth="1" min="4" max="4"/>
-    <ns0:col width="15.63" customWidth="1" min="5" max="5"/>
-    <ns0:col width="10.13" customWidth="1" min="6" max="6"/>
-    <ns0:col width="7.5" customWidth="1" min="7" max="7"/>
-    <ns0:col width="8.880000000000001" customWidth="1" min="8" max="8"/>
-    <ns0:col width="9.75" customWidth="1" min="9" max="9"/>
-    <ns0:col width="9.880000000000001" customWidth="1" min="10" max="10"/>
-    <ns0:col width="10.13" customWidth="1" min="11" max="11"/>
-    <ns0:col width="8.130000000000001" customWidth="1" min="12" max="12"/>
-    <ns0:col width="7.75" customWidth="1" min="13" max="13"/>
-    <ns0:col width="8.880000000000001" customWidth="1" min="14" max="14"/>
-    <ns0:col width="11" customWidth="1" min="15" max="15"/>
-    <ns0:col width="8.25" customWidth="1" min="16" max="16"/>
-    <ns0:col width="10.38" customWidth="1" min="17" max="17"/>
-    <ns0:col width="12.75" customWidth="1" min="18" max="18"/>
-    <ns0:col width="12" customWidth="1" min="19" max="19"/>
-    <ns0:col width="8.25" customWidth="1" min="20" max="20"/>
-    <ns0:col width="9.25" customWidth="1" min="21" max="21"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1">
-      <ns0:c r="A1" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>규칙</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B1" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">한 행 = 플레이어 조작 프로필 하나. Regen은 초당, 시간은 ms, 거리는 타일×100. 1~3열(ID, Name, UnitID)은 Monster·BossState·EliteState와 같은 순서, 그 뒤는 플레이어 전용 열. 약초는 Buff 탭(14001)으로 분리(10/29).
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10.25" customWidth="1" min="1" max="1"/>
+    <col width="6.25" customWidth="1" min="2" max="2"/>
+    <col width="10.13" customWidth="1" min="3" max="3"/>
+    <col width="11.63" customWidth="1" min="4" max="4"/>
+    <col width="15.63" customWidth="1" min="5" max="5"/>
+    <col width="10.13" customWidth="1" min="6" max="6"/>
+    <col width="7.5" customWidth="1" min="7" max="7"/>
+    <col width="8.880000000000001" customWidth="1" min="8" max="8"/>
+    <col width="9.75" customWidth="1" min="9" max="9"/>
+    <col width="9.880000000000001" customWidth="1" min="10" max="10"/>
+    <col width="10.13" customWidth="1" min="11" max="11"/>
+    <col width="8.130000000000001" customWidth="1" min="12" max="12"/>
+    <col width="7.75" customWidth="1" min="13" max="13"/>
+    <col width="8.880000000000001" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="8.25" customWidth="1" min="16" max="16"/>
+    <col width="10.38" customWidth="1" min="17" max="17"/>
+    <col width="12.75" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="8.25" customWidth="1" min="20" max="20"/>
+    <col width="9.25" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>한 행 = 플레이어 조작 프로필 하나. Regen은 초당, 시간은 ms, 거리는 타일×100. 1~3열(ID, Name, UnitID)은 Monster·BossState·EliteState와 같은 순서, 그 뒤는 플레이어 전용 열. 약초는 Buff 탭(14001)으로 분리(10/29).
 [추출 지정 규칙]
 @column Name=UnitID;Type=Integer;Minimum=1;ReferenceTable=UnitStat
 @column Name=StaminaMax;Type=Integer;Minimum=0
@@ -496,332 +496,332 @@
 @column Name=StartWeapon;Type=Integer;Minimum=1;ReferenceTable=Item
 @check Kind=ReferenceValue;Column=UnitID;Table=UnitStat;TargetColumn=Type;Value=Player;Code=UNIT_TYPE
 @check Kind=ReferenceValue;Column=StartWeapon;Table=Item;TargetColumn=ItemType;Value=Weapon;Code=ITEM_TYPE
-@inherit Base=CharacterStat</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C1" s="1" t="n"/>
-      <ns0:c r="D1" s="1" t="n"/>
-      <ns0:c r="E1" s="1" t="n"/>
-      <ns0:c r="F1" s="1" t="n"/>
-      <ns0:c r="G1" s="1" t="n"/>
-      <ns0:c r="H1" s="1" t="n"/>
-      <ns0:c r="I1" s="1" t="n"/>
-      <ns0:c r="J1" s="1" t="n"/>
-      <ns0:c r="K1" s="1" t="n"/>
-      <ns0:c r="L1" s="1" t="n"/>
-      <ns0:c r="M1" s="1" t="n"/>
-      <ns0:c r="N1" s="1" t="n"/>
-      <ns0:c r="O1" s="1" t="n"/>
-      <ns0:c r="P1" s="1" t="n"/>
-      <ns0:c r="Q1" s="1" t="n"/>
-      <ns0:c r="R1" s="1" t="n"/>
-      <ns0:c r="S1" s="2" t="n"/>
-      <ns0:c r="T1" s="2" t="n"/>
-      <ns0:c r="U1" s="2" t="n"/>
-      <ns0:c r="V1" s="2" t="n"/>
-    </ns0:row>
-    <ns0:row r="2">
-      <ns0:c r="A2" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>기능</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B2" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>CSV,스태미나·구르기·점프·피격 경직·착지·매달리기·선입력·시작 무기.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C2" s="1" t="n"/>
-      <ns0:c r="D2" s="1" t="n"/>
-      <ns0:c r="E2" s="1" t="n"/>
-      <ns0:c r="F2" s="1" t="n"/>
-      <ns0:c r="G2" s="1" t="n"/>
-      <ns0:c r="H2" s="1" t="n"/>
-      <ns0:c r="I2" s="1" t="n"/>
-      <ns0:c r="J2" s="1" t="n"/>
-      <ns0:c r="K2" s="1" t="n"/>
-      <ns0:c r="L2" s="1" t="n"/>
-      <ns0:c r="M2" s="1" t="n"/>
-      <ns0:c r="N2" s="1" t="n"/>
-      <ns0:c r="O2" s="1" t="n"/>
-      <ns0:c r="P2" s="1" t="n"/>
-      <ns0:c r="Q2" s="1" t="n"/>
-      <ns0:c r="R2" s="1" t="n"/>
-      <ns0:c r="S2" s="2" t="n"/>
-      <ns0:c r="T2" s="2" t="n"/>
-      <ns0:c r="U2" s="2" t="n"/>
-      <ns0:c r="V2" s="2" t="n"/>
-    </ns0:row>
-    <ns0:row r="3">
-      <ns0:c r="A3" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>역할</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B3" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>플레이어 컨트롤러가 읽는다. UnitID는 UnitStat, StartWeapon은 Item ID.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C3" s="1" t="n"/>
-      <ns0:c r="D3" s="1" t="n"/>
-      <ns0:c r="E3" s="1" t="n"/>
-      <ns0:c r="F3" s="1" t="n"/>
-      <ns0:c r="G3" s="1" t="n"/>
-      <ns0:c r="H3" s="1" t="n"/>
-      <ns0:c r="I3" s="1" t="n"/>
-      <ns0:c r="J3" s="1" t="n"/>
-      <ns0:c r="K3" s="1" t="n"/>
-      <ns0:c r="L3" s="1" t="n"/>
-      <ns0:c r="M3" s="1" t="n"/>
-      <ns0:c r="N3" s="1" t="n"/>
-      <ns0:c r="O3" s="1" t="n"/>
-      <ns0:c r="P3" s="1" t="n"/>
-      <ns0:c r="Q3" s="1" t="n"/>
-      <ns0:c r="R3" s="1" t="n"/>
-      <ns0:c r="S3" s="2" t="n"/>
-      <ns0:c r="T3" s="2" t="n"/>
-      <ns0:c r="U3" s="2" t="n"/>
-      <ns0:c r="V3" s="2" t="n"/>
-    </ns0:row>
-    <ns0:row r="4">
-      <ns0:c r="A4" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>의도</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B4" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>조작 감각을 프로필만 바꿔 비교하기 위해. 인벤토리는 지스타 제외(완성판), 약초 개수만 HUD 표시(Buff 14001 Charges).</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C4" s="1" t="n"/>
-      <ns0:c r="D4" s="1" t="n"/>
-      <ns0:c r="E4" s="1" t="n"/>
-      <ns0:c r="F4" s="1" t="n"/>
-      <ns0:c r="G4" s="1" t="n"/>
-      <ns0:c r="H4" s="1" t="n"/>
-      <ns0:c r="I4" s="1" t="n"/>
-      <ns0:c r="J4" s="1" t="n"/>
-      <ns0:c r="K4" s="1" t="n"/>
-      <ns0:c r="L4" s="1" t="n"/>
-      <ns0:c r="M4" s="1" t="n"/>
-      <ns0:c r="N4" s="1" t="n"/>
-      <ns0:c r="O4" s="1" t="n"/>
-      <ns0:c r="P4" s="1" t="n"/>
-      <ns0:c r="Q4" s="1" t="n"/>
-      <ns0:c r="R4" s="1" t="n"/>
-      <ns0:c r="S4" s="2" t="n"/>
-      <ns0:c r="T4" s="2" t="n"/>
-      <ns0:c r="U4" s="2" t="n"/>
-      <ns0:c r="V4" s="2" t="n"/>
-    </ns0:row>
-    <ns0:row r="5">
-      <ns0:c r="A5" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>비고</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B5" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Name, Note</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C5" s="1" t="n"/>
-      <ns0:c r="D5" s="1" t="n"/>
-      <ns0:c r="E5" s="1" t="n"/>
-      <ns0:c r="F5" s="1" t="n"/>
-      <ns0:c r="G5" s="1" t="n"/>
-      <ns0:c r="H5" s="1" t="n"/>
-      <ns0:c r="I5" s="1" t="n"/>
-      <ns0:c r="J5" s="1" t="n"/>
-      <ns0:c r="K5" s="1" t="n"/>
-      <ns0:c r="L5" s="1" t="n"/>
-      <ns0:c r="M5" s="1" t="n"/>
-      <ns0:c r="N5" s="1" t="n"/>
-      <ns0:c r="O5" s="1" t="n"/>
-      <ns0:c r="P5" s="1" t="n"/>
-      <ns0:c r="Q5" s="1" t="n"/>
-      <ns0:c r="R5" s="1" t="n"/>
-      <ns0:c r="S5" s="2" t="n"/>
-      <ns0:c r="T5" s="2" t="n"/>
-      <ns0:c r="U5" s="2" t="n"/>
-      <ns0:c r="V5" s="2" t="n"/>
-    </ns0:row>
-    <ns0:row r="6">
-      <ns0:c r="A6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>ID</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Name</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>UnitID</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>StaminaMax</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>StaminaRegen</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>StaminaRegenDelay</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="G6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>RollDistance</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>RollTime</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>RollIFrame</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="J6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>RollStamina</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="K6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>JumpHeight</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="L6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>HitStunTime</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>HitIFrame</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="N6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>CritHitStunTime</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="O6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>LandFallHeight</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="P6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>LandTime</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="Q6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>HangAuto</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="R6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>InputBuffer</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="S6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>StartWeapon</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="T6" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Note</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="U6" s="3" t="n"/>
-      <ns0:c r="V6" s="3" t="n"/>
-      <ns0:c r="W6" s="3" t="n"/>
-    </ns0:row>
-    <ns0:row r="7">
-      <ns0:c r="A7" s="4" t="n">
-        <ns0:v>2001</ns0:v>
-      </ns0:c>
-      <ns0:c r="B7" s="4" t="inlineStr">
-        <ns0:is>
-          <ns0:t>막손 기본</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C7" s="4" t="n">
-        <ns0:v>1001</ns0:v>
-      </ns0:c>
-      <ns0:c r="D7" s="4" t="n">
-        <ns0:v>100</ns0:v>
-      </ns0:c>
-      <ns0:c r="E7" s="4" t="n">
-        <ns0:v>45</ns0:v>
-      </ns0:c>
-      <ns0:c r="F7" s="4" t="n">
-        <ns0:v>500</ns0:v>
-      </ns0:c>
-      <ns0:c r="G7" s="4" t="n">
-        <ns0:v>300</ns0:v>
-      </ns0:c>
-      <ns0:c r="H7" s="4" t="n">
-        <ns0:v>500</ns0:v>
-      </ns0:c>
-      <ns0:c r="I7" s="4" t="n">
-        <ns0:v>300</ns0:v>
-      </ns0:c>
-      <ns0:c r="J7" s="4" t="n">
-        <ns0:v>20</ns0:v>
-      </ns0:c>
-      <ns0:c r="K7" s="4" t="n">
-        <ns0:v>300</ns0:v>
-      </ns0:c>
-      <ns0:c r="L7" s="4" t="n">
-        <ns0:v>300</ns0:v>
-      </ns0:c>
-      <ns0:c r="M7" s="4" t="n">
-        <ns0:v>600</ns0:v>
-      </ns0:c>
-      <ns0:c r="N7" s="4" t="n">
-        <ns0:v>500</ns0:v>
-      </ns0:c>
-      <ns0:c r="O7" s="4" t="n">
-        <ns0:v>500</ns0:v>
-      </ns0:c>
-      <ns0:c r="P7" s="4" t="n">
-        <ns0:v>200</ns0:v>
-      </ns0:c>
-      <ns0:c r="Q7" s="4" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Y</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="R7" s="4" t="n">
-        <ns0:v>150</ns0:v>
-      </ns0:c>
-      <ns0:c r="S7" s="4" t="n">
-        <ns0:v>6002</ns0:v>
-      </ns0:c>
-      <ns0:c r="T7" s="4" t="inlineStr">
-        <ns0:is>
-          <ns0:t>CritHitStunTime=치명타 피격 경직, LandFallHeight=착지 모션이 나오는 낙하 높이(5타일), InputBuffer=선입력 버퍼</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-  </ns0:sheetData>
-  <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</ns0:worksheet>
+@inherit Base=CharacterStat</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>CSV,스태미나·구르기·점프·피격 경직·착지·매달리기·선입력·시작 무기.</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>플레이어 컨트롤러가 읽는다. UnitID는 UnitStat, StartWeapon은 Item ID.</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+      <c r="K3" s="1" t="n"/>
+      <c r="L3" s="1" t="n"/>
+      <c r="M3" s="1" t="n"/>
+      <c r="N3" s="1" t="n"/>
+      <c r="O3" s="1" t="n"/>
+      <c r="P3" s="1" t="n"/>
+      <c r="Q3" s="1" t="n"/>
+      <c r="R3" s="1" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>의도</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>조작 감각을 프로필만 바꿔 비교하기 위해. 인벤토리는 지스타 제외(완성판), 약초 개수만 HUD 표시(Buff 14001 Charges).</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="1" t="n"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="G4" s="1" t="n"/>
+      <c r="H4" s="1" t="n"/>
+      <c r="I4" s="1" t="n"/>
+      <c r="J4" s="1" t="n"/>
+      <c r="K4" s="1" t="n"/>
+      <c r="L4" s="1" t="n"/>
+      <c r="M4" s="1" t="n"/>
+      <c r="N4" s="1" t="n"/>
+      <c r="O4" s="1" t="n"/>
+      <c r="P4" s="1" t="n"/>
+      <c r="Q4" s="1" t="n"/>
+      <c r="R4" s="1" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Name, Note</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="n"/>
+      <c r="F5" s="1" t="n"/>
+      <c r="G5" s="1" t="n"/>
+      <c r="H5" s="1" t="n"/>
+      <c r="I5" s="1" t="n"/>
+      <c r="J5" s="1" t="n"/>
+      <c r="K5" s="1" t="n"/>
+      <c r="L5" s="1" t="n"/>
+      <c r="M5" s="1" t="n"/>
+      <c r="N5" s="1" t="n"/>
+      <c r="O5" s="1" t="n"/>
+      <c r="P5" s="1" t="n"/>
+      <c r="Q5" s="1" t="n"/>
+      <c r="R5" s="1" t="n"/>
+      <c r="S5" s="2" t="n"/>
+      <c r="T5" s="2" t="n"/>
+      <c r="U5" s="2" t="n"/>
+      <c r="V5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>UnitID</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>StaminaMax</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>StaminaRegen</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>StaminaRegenDelay</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>RollDistance</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>RollTime</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>RollIFrame</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>RollStamina</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>JumpHeight</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>HitStunTime</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>HitIFrame</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>CritHitStunTime</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>LandFallHeight</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>LandTime</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>HangAuto</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>InputBuffer</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>StartWeapon</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n"/>
+      <c r="W6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>막손 기본</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>6002</v>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>CritHitStunTime=치명타 피격 경직, LandFallHeight=착지 모션이 나오는 낙하 높이(5타일), InputBuffer=선입력 버퍼. HangAuto=N: 매달리기는 버튼 입력(10/30 회의, 자동 잡기 UX 문제)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>